--- a/1015/K800-行业TR分析与达标名单合并表_20261015.xlsx
+++ b/1015/K800-行业TR分析与达标名单合并表_20261015.xlsx
@@ -611,6 +611,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="14">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -650,7 +651,7 @@
     <row r="6" ht="30" customHeight="1" s="14">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>基准定义</t>
+          <t>行业自营TR中位数参考值 = 该行业「自营客户」闭环TR的中位数 × 2 （×2 为加入 1 倍闭环消耗的微信豆预估，与预估TR口径可比）；剔除闭环TR≥100%异常；自营样本&lt;4家回退大盘自营（同口径中位×2）。</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -800,7 +801,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>基准下限</t>
+          <t>行业自营TR中位数参考值</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
@@ -15963,7 +15964,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>基准下限</t>
+          <t>行业自营TR中位数参考值</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -16680,7 +16681,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>基准下限</t>
+          <t>行业自营TR中位数参考值</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -17775,7 +17776,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>基准下限</t>
+          <t>行业自营TR中位数参考值</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -20160,7 +20161,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>基准下限</t>
+          <t>行业自营TR中位数参考值</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -27095,7 +27096,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>基准下限</t>
+          <t>行业自营TR中位数参考值</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -27379,6 +27380,7 @@
         <v>0.2725</v>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
@@ -51220,7 +51222,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>基准下限(中位×2)</t>
+          <t>行业自营TR中位数参考值(=自营闭环TR中位×2)</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
